--- a/corpus/C04.xlsx
+++ b/corpus/C04.xlsx
@@ -752,76 +752,76 @@
         <v>8650.0</v>
       </c>
       <c r="I5">
-        <f>H9</f>
-        <v>8973.0</v>
+        <f>G9</f>
+        <v>8650.0</v>
       </c>
       <c r="J5">
         <f>I9</f>
-        <v>9309.0</v>
+        <v>8973.0</v>
       </c>
       <c r="K5">
         <f>J9</f>
-        <v>9658.0</v>
+        <v>9309.0</v>
       </c>
       <c r="L5">
         <f>K9</f>
-        <v>10019.0</v>
+        <v>9658.0</v>
       </c>
       <c r="M5">
         <f>L9</f>
-        <v>10394.0</v>
+        <v>10019.0</v>
       </c>
       <c r="N5">
         <f>M9</f>
-        <v>10783.0</v>
+        <v>10394.0</v>
       </c>
       <c r="O5">
         <f>N9</f>
-        <v>11186.0</v>
+        <v>10783.0</v>
       </c>
       <c r="P5">
         <f>O9</f>
-        <v>11604.0</v>
+        <v>11186.0</v>
       </c>
       <c r="Q5">
         <f>P9</f>
-        <v>12038.0</v>
+        <v>11604.0</v>
       </c>
       <c r="R5">
         <f>Q9</f>
-        <v>12488.0</v>
+        <v>12038.0</v>
       </c>
       <c r="S5">
         <f>R9</f>
-        <v>12956.0</v>
+        <v>12488.0</v>
       </c>
       <c r="T5">
         <f>S9</f>
-        <v>13441.0</v>
+        <v>12956.0</v>
       </c>
       <c r="U5">
         <f>T9</f>
-        <v>13943.0</v>
+        <v>13441.0</v>
       </c>
       <c r="V5">
         <f>U9</f>
-        <v>14465.0</v>
+        <v>13943.0</v>
       </c>
       <c r="W5">
         <f>V9</f>
-        <v>15006.0</v>
+        <v>14465.0</v>
       </c>
       <c r="X5">
         <f>W9</f>
-        <v>15567.0</v>
+        <v>15006.0</v>
       </c>
       <c r="Y5">
         <f>X9</f>
-        <v>16150.0</v>
+        <v>15567.0</v>
       </c>
       <c r="Z5">
         <f>Y9</f>
-        <v>16754.0</v>
+        <v>16150.0</v>
       </c>
     </row>
     <row r="6">
@@ -856,75 +856,75 @@
       </c>
       <c r="I6">
         <f>ROUND(I5*Assumptions!$B$5,0)</f>
-        <v>525.0</v>
+        <v>506.0</v>
       </c>
       <c r="J6">
         <f>ROUND(J5*Assumptions!$B$5,0)</f>
-        <v>545.0</v>
+        <v>525.0</v>
       </c>
       <c r="K6">
         <f>ROUND(K5*Assumptions!$B$5,0)</f>
-        <v>565.0</v>
+        <v>545.0</v>
       </c>
       <c r="L6">
         <f>ROUND(L5*Assumptions!$B$5,0)</f>
-        <v>586.0</v>
+        <v>565.0</v>
       </c>
       <c r="M6">
         <f>ROUND(M5*Assumptions!$B$5,0)</f>
-        <v>608.0</v>
+        <v>586.0</v>
       </c>
       <c r="N6">
         <f>ROUND(N5*Assumptions!$B$5,0)</f>
-        <v>631.0</v>
+        <v>608.0</v>
       </c>
       <c r="O6">
         <f>ROUND(O5*Assumptions!$B$5,0)</f>
-        <v>654.0</v>
+        <v>631.0</v>
       </c>
       <c r="P6">
         <f>ROUND(P5*Assumptions!$B$5,0)</f>
-        <v>679.0</v>
+        <v>654.0</v>
       </c>
       <c r="Q6">
         <f>ROUND(Q5*Assumptions!$B$5,0)</f>
-        <v>704.0</v>
+        <v>679.0</v>
       </c>
       <c r="R6">
         <f>ROUND(R5*Assumptions!$B$5,0)</f>
-        <v>731.0</v>
+        <v>704.0</v>
       </c>
       <c r="S6">
         <f>ROUND(S5*Assumptions!$B$5,0)</f>
-        <v>758.0</v>
+        <v>731.0</v>
       </c>
       <c r="T6">
         <f>ROUND(T5*Assumptions!$B$5,0)</f>
-        <v>786.0</v>
+        <v>758.0</v>
       </c>
       <c r="U6">
         <f>ROUND(U5*Assumptions!$B$5,0)</f>
-        <v>816.0</v>
+        <v>786.0</v>
       </c>
       <c r="V6">
         <f>ROUND(V5*Assumptions!$B$5,0)</f>
-        <v>846.0</v>
+        <v>816.0</v>
       </c>
       <c r="W6">
         <f>ROUND(W5*Assumptions!$B$5,0)</f>
-        <v>878.0</v>
+        <v>846.0</v>
       </c>
       <c r="X6">
         <f>ROUND(X5*Assumptions!$B$5,0)</f>
-        <v>911.0</v>
+        <v>878.0</v>
       </c>
       <c r="Y6">
         <f>ROUND(Y5*Assumptions!$B$5,0)</f>
-        <v>945.0</v>
+        <v>911.0</v>
       </c>
       <c r="Z6">
         <f>ROUND(Z5*Assumptions!$B$5,0)</f>
-        <v>980.0</v>
+        <v>945.0</v>
       </c>
     </row>
     <row r="7">
@@ -959,75 +959,75 @@
       </c>
       <c r="I7">
         <f>-ROUND(I5*Assumptions!$B$6,0)</f>
-        <v>-189.0</v>
+        <v>-183.0</v>
       </c>
       <c r="J7">
         <f>-ROUND(J5*Assumptions!$B$6,0)</f>
-        <v>-196.0</v>
+        <v>-189.0</v>
       </c>
       <c r="K7">
         <f>-ROUND(K5*Assumptions!$B$6,0)</f>
-        <v>-204.0</v>
+        <v>-196.0</v>
       </c>
       <c r="L7">
         <f>-ROUND(L5*Assumptions!$B$6,0)</f>
-        <v>-211.0</v>
+        <v>-204.0</v>
       </c>
       <c r="M7">
         <f>-ROUND(M5*Assumptions!$B$6,0)</f>
-        <v>-219.0</v>
+        <v>-211.0</v>
       </c>
       <c r="N7">
         <f>-ROUND(N5*Assumptions!$B$6,0)</f>
-        <v>-228.0</v>
+        <v>-219.0</v>
       </c>
       <c r="O7">
         <f>-ROUND(O5*Assumptions!$B$6,0)</f>
-        <v>-236.0</v>
+        <v>-228.0</v>
       </c>
       <c r="P7">
         <f>-ROUND(P5*Assumptions!$B$6,0)</f>
-        <v>-245.0</v>
+        <v>-236.0</v>
       </c>
       <c r="Q7">
         <f>-ROUND(Q5*Assumptions!$B$6,0)</f>
-        <v>-254.0</v>
+        <v>-245.0</v>
       </c>
       <c r="R7">
         <f>-ROUND(R5*Assumptions!$B$6,0)</f>
-        <v>-263.0</v>
+        <v>-254.0</v>
       </c>
       <c r="S7">
         <f>-ROUND(S5*Assumptions!$B$6,0)</f>
-        <v>-273.0</v>
+        <v>-263.0</v>
       </c>
       <c r="T7">
         <f>-ROUND(T5*Assumptions!$B$6,0)</f>
-        <v>-284.0</v>
+        <v>-273.0</v>
       </c>
       <c r="U7">
         <f>-ROUND(U5*Assumptions!$B$6,0)</f>
-        <v>-294.0</v>
+        <v>-284.0</v>
       </c>
       <c r="V7">
         <f>-ROUND(V5*Assumptions!$B$6,0)</f>
-        <v>-305.0</v>
+        <v>-294.0</v>
       </c>
       <c r="W7">
         <f>-ROUND(W5*Assumptions!$B$6,0)</f>
-        <v>-317.0</v>
+        <v>-305.0</v>
       </c>
       <c r="X7">
         <f>-ROUND(X5*Assumptions!$B$6,0)</f>
-        <v>-328.0</v>
+        <v>-317.0</v>
       </c>
       <c r="Y7">
         <f>-ROUND(Y5*Assumptions!$B$6,0)</f>
-        <v>-341.0</v>
+        <v>-328.0</v>
       </c>
       <c r="Z7">
         <f>-ROUND(Z5*Assumptions!$B$6,0)</f>
-        <v>-354.0</v>
+        <v>-341.0</v>
       </c>
     </row>
     <row r="9">
@@ -1062,75 +1062,75 @@
       </c>
       <c r="I9">
         <f>I5+I6+I7</f>
-        <v>9309.0</v>
+        <v>8973.0</v>
       </c>
       <c r="J9">
         <f>J5+J6+J7</f>
-        <v>9658.0</v>
+        <v>9309.0</v>
       </c>
       <c r="K9">
         <f>K5+K6+K7</f>
-        <v>10019.0</v>
+        <v>9658.0</v>
       </c>
       <c r="L9">
         <f>L5+L6+L7</f>
-        <v>10394.0</v>
+        <v>10019.0</v>
       </c>
       <c r="M9">
         <f>M5+M6+M7</f>
-        <v>10783.0</v>
+        <v>10394.0</v>
       </c>
       <c r="N9">
         <f>N5+N6+N7</f>
-        <v>11186.0</v>
+        <v>10783.0</v>
       </c>
       <c r="O9">
         <f>O5+O6+O7</f>
-        <v>11604.0</v>
+        <v>11186.0</v>
       </c>
       <c r="P9">
         <f>P5+P6+P7</f>
-        <v>12038.0</v>
+        <v>11604.0</v>
       </c>
       <c r="Q9">
         <f>Q5+Q6+Q7</f>
-        <v>12488.0</v>
+        <v>12038.0</v>
       </c>
       <c r="R9">
         <f>R5+R6+R7</f>
-        <v>12956.0</v>
+        <v>12488.0</v>
       </c>
       <c r="S9">
         <f>S5+S6+S7</f>
-        <v>13441.0</v>
+        <v>12956.0</v>
       </c>
       <c r="T9">
         <f>T5+T6+T7</f>
-        <v>13943.0</v>
+        <v>13441.0</v>
       </c>
       <c r="U9">
         <f>U5+U6+U7</f>
-        <v>14465.0</v>
+        <v>13943.0</v>
       </c>
       <c r="V9">
         <f>V5+V6+V7</f>
-        <v>15006.0</v>
+        <v>14465.0</v>
       </c>
       <c r="W9">
         <f>W5+W6+W7</f>
-        <v>15567.0</v>
+        <v>15006.0</v>
       </c>
       <c r="X9">
         <f>X5+X6+X7</f>
-        <v>16150.0</v>
+        <v>15567.0</v>
       </c>
       <c r="Y9">
         <f>Y5+Y6+Y7</f>
-        <v>16754.0</v>
+        <v>16150.0</v>
       </c>
       <c r="Z9">
         <f>Z5+Z6+Z7</f>
-        <v>17380.0</v>
+        <v>16754.0</v>
       </c>
     </row>
     <row r="11">
@@ -1268,75 +1268,75 @@
       </c>
       <c r="I13">
         <f>ROUND((I5+I9)/2,0)</f>
-        <v>9141.0</v>
+        <v>8812.0</v>
       </c>
       <c r="J13">
         <f>ROUND((J5+J9)/2,0)</f>
-        <v>9484.0</v>
+        <v>9141.0</v>
       </c>
       <c r="K13">
         <f>ROUND((K5+K9)/2,0)</f>
-        <v>9839.0</v>
+        <v>9484.0</v>
       </c>
       <c r="L13">
         <f>ROUND((L5+L9)/2,0)</f>
-        <v>10207.0</v>
+        <v>9839.0</v>
       </c>
       <c r="M13">
         <f>ROUND((M5+M9)/2,0)</f>
-        <v>10589.0</v>
+        <v>10207.0</v>
       </c>
       <c r="N13">
         <f>ROUND((N5+N9)/2,0)</f>
-        <v>10985.0</v>
+        <v>10589.0</v>
       </c>
       <c r="O13">
         <f>ROUND((O5+O9)/2,0)</f>
-        <v>11395.0</v>
+        <v>10985.0</v>
       </c>
       <c r="P13">
         <f>ROUND((P5+P9)/2,0)</f>
-        <v>11821.0</v>
+        <v>11395.0</v>
       </c>
       <c r="Q13">
         <f>ROUND((Q5+Q9)/2,0)</f>
-        <v>12263.0</v>
+        <v>11821.0</v>
       </c>
       <c r="R13">
         <f>ROUND((R5+R9)/2,0)</f>
-        <v>12722.0</v>
+        <v>12263.0</v>
       </c>
       <c r="S13">
         <f>ROUND((S5+S9)/2,0)</f>
-        <v>13199.0</v>
+        <v>12722.0</v>
       </c>
       <c r="T13">
         <f>ROUND((T5+T9)/2,0)</f>
-        <v>13692.0</v>
+        <v>13199.0</v>
       </c>
       <c r="U13">
         <f>ROUND((U5+U9)/2,0)</f>
-        <v>14204.0</v>
+        <v>13692.0</v>
       </c>
       <c r="V13">
         <f>ROUND((V5+V9)/2,0)</f>
-        <v>14736.0</v>
+        <v>14204.0</v>
       </c>
       <c r="W13">
         <f>ROUND((W5+W9)/2,0)</f>
-        <v>15287.0</v>
+        <v>14736.0</v>
       </c>
       <c r="X13">
         <f>ROUND((X5+X9)/2,0)</f>
-        <v>15859.0</v>
+        <v>15287.0</v>
       </c>
       <c r="Y13">
         <f>ROUND((Y5+Y9)/2,0)</f>
-        <v>16452.0</v>
+        <v>15859.0</v>
       </c>
       <c r="Z13">
         <f>ROUND((Z5+Z9)/2,0)</f>
-        <v>17067.0</v>
+        <v>16452.0</v>
       </c>
     </row>
     <row r="15">
@@ -1371,75 +1371,75 @@
       </c>
       <c r="I15">
         <f>ROUND(I13*I11,0)</f>
-        <v>658152.0</v>
+        <v>634464.0</v>
       </c>
       <c r="J15">
         <f>ROUND(J13*J11,0)</f>
-        <v>685314.0</v>
+        <v>660529.0</v>
       </c>
       <c r="K15">
         <f>ROUND(K13*K11,0)</f>
-        <v>713524.0</v>
+        <v>687780.0</v>
       </c>
       <c r="L15">
         <f>ROUND(L13*L11,0)</f>
-        <v>742865.0</v>
+        <v>716082.0</v>
       </c>
       <c r="M15">
         <f>ROUND(M13*M11,0)</f>
-        <v>773421.0</v>
+        <v>745519.0</v>
       </c>
       <c r="N15">
         <f>ROUND(N13*N11,0)</f>
-        <v>805201.0</v>
+        <v>776174.0</v>
       </c>
       <c r="O15">
         <f>ROUND(O13*O11,0)</f>
-        <v>838216.0</v>
+        <v>808057.0</v>
       </c>
       <c r="P15">
         <f>ROUND(P13*P11,0)</f>
-        <v>872626.0</v>
+        <v>841179.0</v>
       </c>
       <c r="Q15">
         <f>ROUND(Q13*Q11,0)</f>
-        <v>908566.0</v>
+        <v>875818.0</v>
       </c>
       <c r="R15">
         <f>ROUND(R13*R11,0)</f>
-        <v>946008.0</v>
+        <v>911877.0</v>
       </c>
       <c r="S15">
         <f>ROUND(S13*S11,0)</f>
-        <v>985041.0</v>
+        <v>949443.0</v>
       </c>
       <c r="T15">
         <f>ROUND(T13*T11,0)</f>
-        <v>1025531.0</v>
+        <v>988605.0</v>
       </c>
       <c r="U15">
         <f>ROUND(U13*U11,0)</f>
-        <v>1067715.0</v>
+        <v>1029228.0</v>
       </c>
       <c r="V15">
         <f>ROUND(V13*V11,0)</f>
-        <v>1111684.0</v>
+        <v>1071550.0</v>
       </c>
       <c r="W15">
         <f>ROUND(W13*W11,0)</f>
-        <v>1157379.0</v>
+        <v>1115663.0</v>
       </c>
       <c r="X15">
         <f>ROUND(X13*X11,0)</f>
-        <v>1204967.0</v>
+        <v>1161506.0</v>
       </c>
       <c r="Y15">
         <f>ROUND(Y13*Y11,0)</f>
-        <v>1254465.0</v>
+        <v>1209249.0</v>
       </c>
       <c r="Z15">
         <f>ROUND(Z13*Z11,0)</f>
-        <v>1305967.0</v>
+        <v>1258907.0</v>
       </c>
     </row>
     <row r="17">
@@ -1474,75 +1474,75 @@
       </c>
       <c r="I17">
         <f>H17+I15</f>
-        <v>4095568.0</v>
+        <v>4071880.0</v>
       </c>
       <c r="J17">
         <f>I17+J15</f>
-        <v>4780882.0</v>
+        <v>4732409.0</v>
       </c>
       <c r="K17">
         <f>J17+K15</f>
-        <v>5494406.0</v>
+        <v>5420189.0</v>
       </c>
       <c r="L17">
         <f>K17+L15</f>
-        <v>6237271.0</v>
+        <v>6136271.0</v>
       </c>
       <c r="M17">
         <f>L17+M15</f>
-        <v>7010692.0</v>
+        <v>6881790.0</v>
       </c>
       <c r="N17">
         <f>M17+N15</f>
-        <v>7815893.0</v>
+        <v>7657964.0</v>
       </c>
       <c r="O17">
         <f>N17+O15</f>
-        <v>8654109.0</v>
+        <v>8466021.0</v>
       </c>
       <c r="P17">
         <f>O17+P15</f>
-        <v>9526735.0</v>
+        <v>9307200.0</v>
       </c>
       <c r="Q17">
         <f>P17+Q15</f>
-        <v>10435301.0</v>
+        <v>10183018.0</v>
       </c>
       <c r="R17">
         <f>Q17+R15</f>
-        <v>11381309.0</v>
+        <v>11094895.0</v>
       </c>
       <c r="S17">
         <f>R17+S15</f>
-        <v>12366350.0</v>
+        <v>12044338.0</v>
       </c>
       <c r="T17">
         <f>S17+T15</f>
-        <v>13391881.0</v>
+        <v>13032943.0</v>
       </c>
       <c r="U17">
         <f>T17+U15</f>
-        <v>14459596.0</v>
+        <v>14062171.0</v>
       </c>
       <c r="V17">
         <f>U17+V15</f>
-        <v>15571280.0</v>
+        <v>15133721.0</v>
       </c>
       <c r="W17">
         <f>V17+W15</f>
-        <v>16728659.0</v>
+        <v>16249384.0</v>
       </c>
       <c r="X17">
         <f>W17+X15</f>
-        <v>17933626.0</v>
+        <v>17410890.0</v>
       </c>
       <c r="Y17">
         <f>X17+Y15</f>
-        <v>19188091.0</v>
+        <v>18620139.0</v>
       </c>
       <c r="Z17">
         <f>Y17+Z15</f>
-        <v>20494058.0</v>
+        <v>19879046.0</v>
       </c>
     </row>
   </sheetData>
@@ -2113,75 +2113,75 @@
       </c>
       <c r="I10">
         <f>ROUND(Revenue!I15*Assumptions!$B$11,0)</f>
-        <v>169013.0</v>
+        <v>162930.0</v>
       </c>
       <c r="J10">
         <f>ROUND(Revenue!J15*Assumptions!$B$11,0)</f>
-        <v>175989.0</v>
+        <v>169624.0</v>
       </c>
       <c r="K10">
         <f>ROUND(Revenue!K15*Assumptions!$B$11,0)</f>
-        <v>183233.0</v>
+        <v>176622.0</v>
       </c>
       <c r="L10">
         <f>ROUND(Revenue!L15*Assumptions!$B$11,0)</f>
-        <v>190768.0</v>
+        <v>183890.0</v>
       </c>
       <c r="M10">
         <f>ROUND(Revenue!M15*Assumptions!$B$11,0)</f>
-        <v>198615.0</v>
+        <v>191449.0</v>
       </c>
       <c r="N10">
         <f>ROUND(Revenue!N15*Assumptions!$B$11,0)</f>
-        <v>206776.0</v>
+        <v>199321.0</v>
       </c>
       <c r="O10">
         <f>ROUND(Revenue!O15*Assumptions!$B$11,0)</f>
-        <v>215254.0</v>
+        <v>207509.0</v>
       </c>
       <c r="P10">
         <f>ROUND(Revenue!P15*Assumptions!$B$11,0)</f>
-        <v>224090.0</v>
+        <v>216015.0</v>
       </c>
       <c r="Q10">
         <f>ROUND(Revenue!Q15*Assumptions!$B$11,0)</f>
-        <v>233320.0</v>
+        <v>224910.0</v>
       </c>
       <c r="R10">
         <f>ROUND(Revenue!R15*Assumptions!$B$11,0)</f>
-        <v>242935.0</v>
+        <v>234170.0</v>
       </c>
       <c r="S10">
         <f>ROUND(Revenue!S15*Assumptions!$B$11,0)</f>
-        <v>252959.0</v>
+        <v>243817.0</v>
       </c>
       <c r="T10">
         <f>ROUND(Revenue!T15*Assumptions!$B$11,0)</f>
-        <v>263356.0</v>
+        <v>253874.0</v>
       </c>
       <c r="U10">
         <f>ROUND(Revenue!U15*Assumptions!$B$11,0)</f>
-        <v>274189.0</v>
+        <v>264306.0</v>
       </c>
       <c r="V10">
         <f>ROUND(Revenue!V15*Assumptions!$B$11,0)</f>
-        <v>285480.0</v>
+        <v>275174.0</v>
       </c>
       <c r="W10">
         <f>ROUND(Revenue!W15*Assumptions!$B$11,0)</f>
-        <v>297215.0</v>
+        <v>286502.0</v>
       </c>
       <c r="X10">
         <f>ROUND(Revenue!X15*Assumptions!$B$11,0)</f>
-        <v>309436.0</v>
+        <v>298275.0</v>
       </c>
       <c r="Y10">
         <f>ROUND(Revenue!Y15*Assumptions!$B$11,0)</f>
-        <v>322147.0</v>
+        <v>310535.0</v>
       </c>
       <c r="Z10">
         <f>ROUND(Revenue!Z15*Assumptions!$B$11,0)</f>
-        <v>335372.0</v>
+        <v>323287.0</v>
       </c>
     </row>
     <row r="11">
@@ -2216,75 +2216,75 @@
       </c>
       <c r="I11">
         <f>ROUND(Revenue!I15*Assumptions!$B$16,0)</f>
-        <v>79044.0</v>
+        <v>76199.0</v>
       </c>
       <c r="J11">
         <f>ROUND(Revenue!J15*Assumptions!$B$16,0)</f>
-        <v>82306.0</v>
+        <v>79330.0</v>
       </c>
       <c r="K11">
         <f>ROUND(Revenue!K15*Assumptions!$B$16,0)</f>
-        <v>85694.0</v>
+        <v>82602.0</v>
       </c>
       <c r="L11">
         <f>ROUND(Revenue!L15*Assumptions!$B$16,0)</f>
-        <v>89218.0</v>
+        <v>86001.0</v>
       </c>
       <c r="M11">
         <f>ROUND(Revenue!M15*Assumptions!$B$16,0)</f>
-        <v>92888.0</v>
+        <v>89537.0</v>
       </c>
       <c r="N11">
         <f>ROUND(Revenue!N15*Assumptions!$B$16,0)</f>
-        <v>96705.0</v>
+        <v>93218.0</v>
       </c>
       <c r="O11">
         <f>ROUND(Revenue!O15*Assumptions!$B$16,0)</f>
-        <v>100670.0</v>
+        <v>97048.0</v>
       </c>
       <c r="P11">
         <f>ROUND(Revenue!P15*Assumptions!$B$16,0)</f>
-        <v>104802.0</v>
+        <v>101026.0</v>
       </c>
       <c r="Q11">
         <f>ROUND(Revenue!Q15*Assumptions!$B$16,0)</f>
-        <v>109119.0</v>
+        <v>105186.0</v>
       </c>
       <c r="R11">
         <f>ROUND(Revenue!R15*Assumptions!$B$16,0)</f>
-        <v>113616.0</v>
+        <v>109516.0</v>
       </c>
       <c r="S11">
         <f>ROUND(Revenue!S15*Assumptions!$B$16,0)</f>
-        <v>118303.0</v>
+        <v>114028.0</v>
       </c>
       <c r="T11">
         <f>ROUND(Revenue!T15*Assumptions!$B$16,0)</f>
-        <v>123166.0</v>
+        <v>118731.0</v>
       </c>
       <c r="U11">
         <f>ROUND(Revenue!U15*Assumptions!$B$16,0)</f>
-        <v>128233.0</v>
+        <v>123610.0</v>
       </c>
       <c r="V11">
         <f>ROUND(Revenue!V15*Assumptions!$B$16,0)</f>
-        <v>133513.0</v>
+        <v>128693.0</v>
       </c>
       <c r="W11">
         <f>ROUND(Revenue!W15*Assumptions!$B$16,0)</f>
-        <v>139001.0</v>
+        <v>133991.0</v>
       </c>
       <c r="X11">
         <f>ROUND(Revenue!X15*Assumptions!$B$16,0)</f>
-        <v>144717.0</v>
+        <v>139497.0</v>
       </c>
       <c r="Y11">
         <f>ROUND(Revenue!Y15*Assumptions!$B$16,0)</f>
-        <v>150661.0</v>
+        <v>145231.0</v>
       </c>
       <c r="Z11">
         <f>ROUND(Revenue!Z15*Assumptions!$B$16,0)</f>
-        <v>156847.0</v>
+        <v>151195.0</v>
       </c>
     </row>
     <row r="12">
@@ -2422,75 +2422,75 @@
       </c>
       <c r="I14">
         <f>I8+I10+I11+I12</f>
-        <v>417831.0</v>
+        <v>408903.0</v>
       </c>
       <c r="J14">
         <f>J8+J10+J11+J12</f>
-        <v>439263.0</v>
+        <v>429922.0</v>
       </c>
       <c r="K14">
         <f>K8+K10+K11+K12</f>
-        <v>461090.0</v>
+        <v>451387.0</v>
       </c>
       <c r="L14">
         <f>L8+L10+L11+L12</f>
-        <v>483345.0</v>
+        <v>473250.0</v>
       </c>
       <c r="M14">
         <f>M8+M10+M11+M12</f>
-        <v>506060.0</v>
+        <v>495543.0</v>
       </c>
       <c r="N14">
         <f>N8+N10+N11+N12</f>
-        <v>529237.0</v>
+        <v>518295.0</v>
       </c>
       <c r="O14">
         <f>O8+O10+O11+O12</f>
-        <v>552880.0</v>
+        <v>541513.0</v>
       </c>
       <c r="P14">
         <f>P8+P10+P11+P12</f>
-        <v>577049.0</v>
+        <v>565198.0</v>
       </c>
       <c r="Q14">
         <f>Q8+Q10+Q11+Q12</f>
-        <v>601798.0</v>
+        <v>589455.0</v>
       </c>
       <c r="R14">
         <f>R8+R10+R11+R12</f>
-        <v>627114.0</v>
+        <v>614249.0</v>
       </c>
       <c r="S14">
         <f>S8+S10+S11+S12</f>
-        <v>653030.0</v>
+        <v>639613.0</v>
       </c>
       <c r="T14">
         <f>T8+T10+T11+T12</f>
-        <v>679496.0</v>
+        <v>665579.0</v>
       </c>
       <c r="U14">
         <f>U8+U10+U11+U12</f>
-        <v>706603.0</v>
+        <v>692097.0</v>
       </c>
       <c r="V14">
         <f>V8+V10+V11+V12</f>
-        <v>734382.0</v>
+        <v>719256.0</v>
       </c>
       <c r="W14">
         <f>W8+W10+W11+W12</f>
-        <v>762815.0</v>
+        <v>747092.0</v>
       </c>
       <c r="X14">
         <f>X8+X10+X11+X12</f>
-        <v>791963.0</v>
+        <v>775582.0</v>
       </c>
       <c r="Y14">
         <f>Y8+Y10+Y11+Y12</f>
-        <v>821830.0</v>
+        <v>804788.0</v>
       </c>
       <c r="Z14">
         <f>Z8+Z10+Z11+Z12</f>
-        <v>852455.0</v>
+        <v>834718.0</v>
       </c>
     </row>
   </sheetData>
@@ -2654,79 +2654,79 @@
       </c>
       <c r="I5">
         <f>Revenue!I15</f>
-        <v>658152.0</v>
+        <v>634464.0</v>
       </c>
       <c r="J5">
         <f>Revenue!J15</f>
-        <v>685314.0</v>
+        <v>660529.0</v>
       </c>
       <c r="K5">
         <f>Revenue!K15</f>
-        <v>713524.0</v>
+        <v>687780.0</v>
       </c>
       <c r="L5">
         <f>Revenue!L15</f>
-        <v>742865.0</v>
+        <v>716082.0</v>
       </c>
       <c r="M5">
         <f>Revenue!M15</f>
-        <v>773421.0</v>
+        <v>745519.0</v>
       </c>
       <c r="N5">
         <f>Revenue!N15</f>
-        <v>805201.0</v>
+        <v>776174.0</v>
       </c>
       <c r="O5">
         <f>Revenue!O15</f>
-        <v>838216.0</v>
+        <v>808057.0</v>
       </c>
       <c r="P5">
         <f>Revenue!P15</f>
-        <v>872626.0</v>
+        <v>841179.0</v>
       </c>
       <c r="Q5">
         <f>Revenue!Q15</f>
-        <v>908566.0</v>
+        <v>875818.0</v>
       </c>
       <c r="R5">
         <f>Revenue!R15</f>
-        <v>946008.0</v>
+        <v>911877.0</v>
       </c>
       <c r="S5">
         <f>Revenue!S15</f>
-        <v>985041.0</v>
+        <v>949443.0</v>
       </c>
       <c r="T5">
         <f>Revenue!T15</f>
-        <v>1025531.0</v>
+        <v>988605.0</v>
       </c>
       <c r="U5">
         <f>Revenue!U15</f>
-        <v>1067715.0</v>
+        <v>1029228.0</v>
       </c>
       <c r="V5">
         <f>Revenue!V15</f>
-        <v>1111684.0</v>
+        <v>1071550.0</v>
       </c>
       <c r="W5">
         <f>Revenue!W15</f>
-        <v>1157379.0</v>
+        <v>1115663.0</v>
       </c>
       <c r="X5">
         <f>Revenue!X15</f>
-        <v>1204967.0</v>
+        <v>1161506.0</v>
       </c>
       <c r="Y5">
         <f>Revenue!Y15</f>
-        <v>1254465.0</v>
+        <v>1209249.0</v>
       </c>
       <c r="Z5">
         <f>Revenue!Z15</f>
-        <v>1305967.0</v>
+        <v>1258907.0</v>
       </c>
       <c r="AA5">
         <f>SUM(C5:Z5)</f>
-        <v>20494058.0</v>
+        <v>19879046.0</v>
       </c>
     </row>
     <row r="6">
@@ -2761,79 +2761,79 @@
       </c>
       <c r="I6">
         <f>-Costs!I10</f>
-        <v>-169013.0</v>
+        <v>-162930.0</v>
       </c>
       <c r="J6">
         <f>-Costs!J10</f>
-        <v>-175989.0</v>
+        <v>-169624.0</v>
       </c>
       <c r="K6">
         <f>-Costs!K10</f>
-        <v>-183233.0</v>
+        <v>-176622.0</v>
       </c>
       <c r="L6">
         <f>-Costs!L10</f>
-        <v>-190768.0</v>
+        <v>-183890.0</v>
       </c>
       <c r="M6">
         <f>-Costs!M10</f>
-        <v>-198615.0</v>
+        <v>-191449.0</v>
       </c>
       <c r="N6">
         <f>-Costs!N10</f>
-        <v>-206776.0</v>
+        <v>-199321.0</v>
       </c>
       <c r="O6">
         <f>-Costs!O10</f>
-        <v>-215254.0</v>
+        <v>-207509.0</v>
       </c>
       <c r="P6">
         <f>-Costs!P10</f>
-        <v>-224090.0</v>
+        <v>-216015.0</v>
       </c>
       <c r="Q6">
         <f>-Costs!Q10</f>
-        <v>-233320.0</v>
+        <v>-224910.0</v>
       </c>
       <c r="R6">
         <f>-Costs!R10</f>
-        <v>-242935.0</v>
+        <v>-234170.0</v>
       </c>
       <c r="S6">
         <f>-Costs!S10</f>
-        <v>-252959.0</v>
+        <v>-243817.0</v>
       </c>
       <c r="T6">
         <f>-Costs!T10</f>
-        <v>-263356.0</v>
+        <v>-253874.0</v>
       </c>
       <c r="U6">
         <f>-Costs!U10</f>
-        <v>-274189.0</v>
+        <v>-264306.0</v>
       </c>
       <c r="V6">
         <f>-Costs!V10</f>
-        <v>-285480.0</v>
+        <v>-275174.0</v>
       </c>
       <c r="W6">
         <f>-Costs!W10</f>
-        <v>-297215.0</v>
+        <v>-286502.0</v>
       </c>
       <c r="X6">
         <f>-Costs!X10</f>
-        <v>-309436.0</v>
+        <v>-298275.0</v>
       </c>
       <c r="Y6">
         <f>-Costs!Y10</f>
-        <v>-322147.0</v>
+        <v>-310535.0</v>
       </c>
       <c r="Z6">
         <f>-Costs!Z10</f>
-        <v>-335372.0</v>
+        <v>-323287.0</v>
       </c>
       <c r="AA6">
         <f>SUM(C6:Z6)</f>
-        <v>-5262875.0</v>
+        <v>-5104938.0</v>
       </c>
     </row>
     <row r="7">
@@ -2868,79 +2868,79 @@
       </c>
       <c r="I7">
         <f>I5+I6</f>
-        <v>489139.0</v>
+        <v>471534.0</v>
       </c>
       <c r="J7">
         <f>J5+J6</f>
-        <v>509325.0</v>
+        <v>490905.0</v>
       </c>
       <c r="K7">
         <f>K5+K6</f>
-        <v>530291.0</v>
+        <v>511158.0</v>
       </c>
       <c r="L7">
         <f>L5+L6</f>
-        <v>552097.0</v>
+        <v>532192.0</v>
       </c>
       <c r="M7">
         <f>M5+M6</f>
-        <v>574806.0</v>
+        <v>554070.0</v>
       </c>
       <c r="N7">
         <f>N5+N6</f>
-        <v>598425.0</v>
+        <v>576853.0</v>
       </c>
       <c r="O7">
         <f>O5+O6</f>
-        <v>622962.0</v>
+        <v>600548.0</v>
       </c>
       <c r="P7">
         <f>P5+P6</f>
-        <v>648536.0</v>
+        <v>625164.0</v>
       </c>
       <c r="Q7">
         <f>Q5+Q6</f>
-        <v>675246.0</v>
+        <v>650908.0</v>
       </c>
       <c r="R7">
         <f>R5+R6</f>
-        <v>703073.0</v>
+        <v>677707.0</v>
       </c>
       <c r="S7">
         <f>S5+S6</f>
-        <v>732082.0</v>
+        <v>705626.0</v>
       </c>
       <c r="T7">
         <f>T5+T6</f>
-        <v>762175.0</v>
+        <v>734731.0</v>
       </c>
       <c r="U7">
         <f>U5+U6</f>
-        <v>793526.0</v>
+        <v>764922.0</v>
       </c>
       <c r="V7">
         <f>V5+V6</f>
-        <v>826204.0</v>
+        <v>796376.0</v>
       </c>
       <c r="W7">
         <f>W5+W6</f>
-        <v>860164.0</v>
+        <v>829161.0</v>
       </c>
       <c r="X7">
         <f>X5+X6</f>
-        <v>895531.0</v>
+        <v>863231.0</v>
       </c>
       <c r="Y7">
         <f>Y5+Y6</f>
-        <v>932318.0</v>
+        <v>898714.0</v>
       </c>
       <c r="Z7">
         <f>Z5+Z6</f>
-        <v>970595.0</v>
+        <v>935620.0</v>
       </c>
       <c r="AA7">
         <f>SUM(C7:Z7)</f>
-        <v>15231183.0</v>
+        <v>14774108.0</v>
       </c>
     </row>
     <row r="8">
@@ -3185,79 +3185,79 @@
       </c>
       <c r="I11">
         <f>-Costs!I11</f>
-        <v>-79044.0</v>
+        <v>-76199.0</v>
       </c>
       <c r="J11">
         <f>-Costs!J11</f>
-        <v>-82306.0</v>
+        <v>-79330.0</v>
       </c>
       <c r="K11">
         <f>-Costs!K11</f>
-        <v>-85694.0</v>
+        <v>-82602.0</v>
       </c>
       <c r="L11">
         <f>-Costs!L11</f>
-        <v>-89218.0</v>
+        <v>-86001.0</v>
       </c>
       <c r="M11">
         <f>-Costs!M11</f>
-        <v>-92888.0</v>
+        <v>-89537.0</v>
       </c>
       <c r="N11">
         <f>-Costs!N11</f>
-        <v>-96705.0</v>
+        <v>-93218.0</v>
       </c>
       <c r="O11">
         <f>-Costs!O11</f>
-        <v>-100670.0</v>
+        <v>-97048.0</v>
       </c>
       <c r="P11">
         <f>-Costs!P11</f>
-        <v>-104802.0</v>
+        <v>-101026.0</v>
       </c>
       <c r="Q11">
         <f>-Costs!Q11</f>
-        <v>-109119.0</v>
+        <v>-105186.0</v>
       </c>
       <c r="R11">
         <f>-Costs!R11</f>
-        <v>-113616.0</v>
+        <v>-109516.0</v>
       </c>
       <c r="S11">
         <f>-Costs!S11</f>
-        <v>-118303.0</v>
+        <v>-114028.0</v>
       </c>
       <c r="T11">
         <f>-Costs!T11</f>
-        <v>-123166.0</v>
+        <v>-118731.0</v>
       </c>
       <c r="U11">
         <f>-Costs!U11</f>
-        <v>-128233.0</v>
+        <v>-123610.0</v>
       </c>
       <c r="V11">
         <f>-Costs!V11</f>
-        <v>-133513.0</v>
+        <v>-128693.0</v>
       </c>
       <c r="W11">
         <f>-Costs!W11</f>
-        <v>-139001.0</v>
+        <v>-133991.0</v>
       </c>
       <c r="X11">
         <f>-Costs!X11</f>
-        <v>-144717.0</v>
+        <v>-139497.0</v>
       </c>
       <c r="Y11">
         <f>-Costs!Y11</f>
-        <v>-150661.0</v>
+        <v>-145231.0</v>
       </c>
       <c r="Z11">
         <f>-Costs!Z11</f>
-        <v>-156847.0</v>
+        <v>-151195.0</v>
       </c>
       <c r="AA11">
         <f>SUM(C11:Z11)</f>
-        <v>-2461337.0</v>
+        <v>-2387473.0</v>
       </c>
     </row>
     <row r="12">
@@ -3399,79 +3399,79 @@
       </c>
       <c r="I13">
         <f>I10+I11+I12</f>
-        <v>-248818.0</v>
+        <v>-245973.0</v>
       </c>
       <c r="J13">
         <f>J10+J11+J12</f>
-        <v>-263274.0</v>
+        <v>-260298.0</v>
       </c>
       <c r="K13">
         <f>K10+K11+K12</f>
-        <v>-277857.0</v>
+        <v>-274765.0</v>
       </c>
       <c r="L13">
         <f>L10+L11+L12</f>
-        <v>-292577.0</v>
+        <v>-289360.0</v>
       </c>
       <c r="M13">
         <f>M10+M11+M12</f>
-        <v>-307445.0</v>
+        <v>-304094.0</v>
       </c>
       <c r="N13">
         <f>N10+N11+N12</f>
-        <v>-322461.0</v>
+        <v>-318974.0</v>
       </c>
       <c r="O13">
         <f>O10+O11+O12</f>
-        <v>-337626.0</v>
+        <v>-334004.0</v>
       </c>
       <c r="P13">
         <f>P10+P11+P12</f>
-        <v>-352959.0</v>
+        <v>-349183.0</v>
       </c>
       <c r="Q13">
         <f>Q10+Q11+Q12</f>
-        <v>-368478.0</v>
+        <v>-364545.0</v>
       </c>
       <c r="R13">
         <f>R10+R11+R12</f>
-        <v>-384179.0</v>
+        <v>-380079.0</v>
       </c>
       <c r="S13">
         <f>S10+S11+S12</f>
-        <v>-400071.0</v>
+        <v>-395796.0</v>
       </c>
       <c r="T13">
         <f>T10+T11+T12</f>
-        <v>-416140.0</v>
+        <v>-411705.0</v>
       </c>
       <c r="U13">
         <f>U10+U11+U12</f>
-        <v>-432414.0</v>
+        <v>-427791.0</v>
       </c>
       <c r="V13">
         <f>V10+V11+V12</f>
-        <v>-448902.0</v>
+        <v>-444082.0</v>
       </c>
       <c r="W13">
         <f>W10+W11+W12</f>
-        <v>-465600.0</v>
+        <v>-460590.0</v>
       </c>
       <c r="X13">
         <f>X10+X11+X12</f>
-        <v>-482527.0</v>
+        <v>-477307.0</v>
       </c>
       <c r="Y13">
         <f>Y10+Y11+Y12</f>
-        <v>-499683.0</v>
+        <v>-494253.0</v>
       </c>
       <c r="Z13">
         <f>Z10+Z11+Z12</f>
-        <v>-517083.0</v>
+        <v>-511431.0</v>
       </c>
       <c r="AA13">
         <f>SUM(C13:Z13)</f>
-        <v>-8014557.0</v>
+        <v>-7940693.0</v>
       </c>
     </row>
     <row r="15">
@@ -3506,79 +3506,79 @@
       </c>
       <c r="I15">
         <f>I7+I13</f>
-        <v>240321.0</v>
+        <v>225561.0</v>
       </c>
       <c r="J15">
         <f>J7+J13</f>
-        <v>246051.0</v>
+        <v>230607.0</v>
       </c>
       <c r="K15">
         <f>K7+K13</f>
-        <v>252434.0</v>
+        <v>236393.0</v>
       </c>
       <c r="L15">
         <f>L7+L13</f>
-        <v>259520.0</v>
+        <v>242832.0</v>
       </c>
       <c r="M15">
         <f>M7+M13</f>
-        <v>267361.0</v>
+        <v>249976.0</v>
       </c>
       <c r="N15">
         <f>N7+N13</f>
-        <v>275964.0</v>
+        <v>257879.0</v>
       </c>
       <c r="O15">
         <f>O7+O13</f>
-        <v>285336.0</v>
+        <v>266544.0</v>
       </c>
       <c r="P15">
         <f>P7+P13</f>
-        <v>295577.0</v>
+        <v>275981.0</v>
       </c>
       <c r="Q15">
         <f>Q7+Q13</f>
-        <v>306768.0</v>
+        <v>286363.0</v>
       </c>
       <c r="R15">
         <f>R7+R13</f>
-        <v>318894.0</v>
+        <v>297628.0</v>
       </c>
       <c r="S15">
         <f>S7+S13</f>
-        <v>332011.0</v>
+        <v>309830.0</v>
       </c>
       <c r="T15">
         <f>T7+T13</f>
-        <v>346035.0</v>
+        <v>323026.0</v>
       </c>
       <c r="U15">
         <f>U7+U13</f>
-        <v>361112.0</v>
+        <v>337131.0</v>
       </c>
       <c r="V15">
         <f>V7+V13</f>
-        <v>377302.0</v>
+        <v>352294.0</v>
       </c>
       <c r="W15">
         <f>W7+W13</f>
-        <v>394564.0</v>
+        <v>368571.0</v>
       </c>
       <c r="X15">
         <f>X7+X13</f>
-        <v>413004.0</v>
+        <v>385924.0</v>
       </c>
       <c r="Y15">
         <f>Y7+Y13</f>
-        <v>432635.0</v>
+        <v>404461.0</v>
       </c>
       <c r="Z15">
         <f>Z7+Z13</f>
-        <v>453512.0</v>
+        <v>424189.0</v>
       </c>
       <c r="AA15">
         <f>SUM(C15:Z15)</f>
-        <v>7216626.0</v>
+        <v>6833415.0</v>
       </c>
     </row>
     <row r="16">
@@ -3613,75 +3613,75 @@
       </c>
       <c r="I16">
         <f>IF(I5=0,0,ROUND(I15/I5,4))</f>
-        <v>0.3651</v>
+        <v>0.3555</v>
       </c>
       <c r="J16">
         <f>IF(J5=0,0,ROUND(J15/J5,4))</f>
-        <v>0.359</v>
+        <v>0.3491</v>
       </c>
       <c r="K16">
         <f>IF(K5=0,0,ROUND(K15/K5,4))</f>
-        <v>0.3538</v>
+        <v>0.3437</v>
       </c>
       <c r="L16">
         <f>IF(L5=0,0,ROUND(L15/L5,4))</f>
-        <v>0.3494</v>
+        <v>0.3391</v>
       </c>
       <c r="M16">
         <f>IF(M5=0,0,ROUND(M15/M5,4))</f>
-        <v>0.3457</v>
+        <v>0.3353</v>
       </c>
       <c r="N16">
         <f>IF(N5=0,0,ROUND(N15/N5,4))</f>
-        <v>0.3427</v>
+        <v>0.3322</v>
       </c>
       <c r="O16">
         <f>IF(O5=0,0,ROUND(O15/O5,4))</f>
-        <v>0.3404</v>
+        <v>0.3299</v>
       </c>
       <c r="P16">
         <f>IF(P5=0,0,ROUND(P15/P5,4))</f>
-        <v>0.3387</v>
+        <v>0.3281</v>
       </c>
       <c r="Q16">
         <f>IF(Q5=0,0,ROUND(Q15/Q5,4))</f>
-        <v>0.3376</v>
+        <v>0.327</v>
       </c>
       <c r="R16">
         <f>IF(R5=0,0,ROUND(R15/R5,4))</f>
-        <v>0.3371</v>
+        <v>0.3264</v>
       </c>
       <c r="S16">
         <f>IF(S5=0,0,ROUND(S15/S5,4))</f>
-        <v>0.3371</v>
+        <v>0.3263</v>
       </c>
       <c r="T16">
         <f>IF(T5=0,0,ROUND(T15/T5,4))</f>
-        <v>0.3374</v>
+        <v>0.3267</v>
       </c>
       <c r="U16">
         <f>IF(U5=0,0,ROUND(U15/U5,4))</f>
-        <v>0.3382</v>
+        <v>0.3276</v>
       </c>
       <c r="V16">
         <f>IF(V5=0,0,ROUND(V15/V5,4))</f>
-        <v>0.3394</v>
+        <v>0.3288</v>
       </c>
       <c r="W16">
         <f>IF(W5=0,0,ROUND(W15/W5,4))</f>
-        <v>0.3409</v>
+        <v>0.3304</v>
       </c>
       <c r="X16">
         <f>IF(X5=0,0,ROUND(X15/X5,4))</f>
-        <v>0.3428</v>
+        <v>0.3323</v>
       </c>
       <c r="Y16">
         <f>IF(Y5=0,0,ROUND(Y15/Y5,4))</f>
-        <v>0.3449</v>
+        <v>0.3345</v>
       </c>
       <c r="Z16">
         <f>IF(Z5=0,0,ROUND(Z15/Z5,4))</f>
-        <v>0.3473</v>
+        <v>0.337</v>
       </c>
     </row>
     <row r="18">
@@ -3716,75 +3716,75 @@
       </c>
       <c r="I18">
         <f>H18+I15</f>
-        <v>1598546.0</v>
+        <v>1583786.0</v>
       </c>
       <c r="J18">
         <f>I18+J15</f>
-        <v>1844597.0</v>
+        <v>1814393.0</v>
       </c>
       <c r="K18">
         <f>J18+K15</f>
-        <v>2097031.0</v>
+        <v>2050786.0</v>
       </c>
       <c r="L18">
         <f>K18+L15</f>
-        <v>2356551.0</v>
+        <v>2293618.0</v>
       </c>
       <c r="M18">
         <f>L18+M15</f>
-        <v>2623912.0</v>
+        <v>2543594.0</v>
       </c>
       <c r="N18">
         <f>M18+N15</f>
-        <v>2899876.0</v>
+        <v>2801473.0</v>
       </c>
       <c r="O18">
         <f>N18+O15</f>
-        <v>3185212.0</v>
+        <v>3068017.0</v>
       </c>
       <c r="P18">
         <f>O18+P15</f>
-        <v>3480789.0</v>
+        <v>3343998.0</v>
       </c>
       <c r="Q18">
         <f>P18+Q15</f>
-        <v>3787557.0</v>
+        <v>3630361.0</v>
       </c>
       <c r="R18">
         <f>Q18+R15</f>
-        <v>4106451.0</v>
+        <v>3927989.0</v>
       </c>
       <c r="S18">
         <f>R18+S15</f>
-        <v>4438462.0</v>
+        <v>4237819.0</v>
       </c>
       <c r="T18">
         <f>S18+T15</f>
-        <v>4784497.0</v>
+        <v>4560845.0</v>
       </c>
       <c r="U18">
         <f>T18+U15</f>
-        <v>5145609.0</v>
+        <v>4897976.0</v>
       </c>
       <c r="V18">
         <f>U18+V15</f>
-        <v>5522911.0</v>
+        <v>5250270.0</v>
       </c>
       <c r="W18">
         <f>V18+W15</f>
-        <v>5917475.0</v>
+        <v>5618841.0</v>
       </c>
       <c r="X18">
         <f>W18+X15</f>
-        <v>6330479.0</v>
+        <v>6004765.0</v>
       </c>
       <c r="Y18">
         <f>X18+Y15</f>
-        <v>6763114.0</v>
+        <v>6409226.0</v>
       </c>
       <c r="Z18">
         <f>Y18+Z15</f>
-        <v>7216626.0</v>
+        <v>6833415.0</v>
       </c>
     </row>
   </sheetData>
@@ -3816,7 +3816,7 @@
       </c>
       <c r="B3">
         <f>Revenue!Z17</f>
-        <v>20494058.0</v>
+        <v>19879046.0</v>
       </c>
     </row>
     <row r="4">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="B4">
         <f>'P&amp;L'!AA15</f>
-        <v>7216626.0</v>
+        <v>6833415.0</v>
       </c>
     </row>
     <row r="5">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="B5">
         <f>SUM('P&amp;L'!O15:Z15)</f>
-        <v>4316750.0</v>
+        <v>4031942.0</v>
       </c>
     </row>
     <row r="6">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="B7">
         <f>ROUND(B5*B6,0)</f>
-        <v>53959375.0</v>
+        <v>50399275.0</v>
       </c>
     </row>
     <row r="8">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="B9">
         <f>B7-B8</f>
-        <v>52009375.0</v>
+        <v>48449275.0</v>
       </c>
     </row>
     <row r="11">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="B11">
         <f>AVERAGE('P&amp;L'!C15:Z15)</f>
-        <v>300692.75</v>
+        <v>284725.625</v>
       </c>
     </row>
     <row r="12">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="B12">
         <f>MAX('P&amp;L'!C15:Z15)</f>
-        <v>453512.0</v>
+        <v>424189.0</v>
       </c>
     </row>
     <row r="13">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="B14">
         <f>SUMIF('P&amp;L'!C15:Z15,"&gt;0")</f>
-        <v>7216626.0</v>
+        <v>6833415.0</v>
       </c>
     </row>
     <row r="15">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="B15">
         <f>ABS(B12-B13)</f>
-        <v>234112.0</v>
+        <v>204789.0</v>
       </c>
     </row>
   </sheetData>
